--- a/office/data/工资收入.xlsx
+++ b/office/data/工资收入.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\office\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C2293F-EECE-4BA9-BB29-208F104D49F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6C9A387-E1B3-4A5F-8E1C-4D3F790E59A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工资表" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <definedName name="工资" localSheetId="2">frequency!$A$1:$G$11</definedName>
     <definedName name="工资">工资表!$A$1:$G$11</definedName>
     <definedName name="_xlnm.Extract" localSheetId="2">frequency!$B$15:$I$15</definedName>
-    <definedName name="_xlnm.Extract" localSheetId="0">工资表!$L$15:$S$15</definedName>
+    <definedName name="_xlnm.Extract" localSheetId="0">工资表!$K$8:$R$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -565,10 +565,6 @@
       <c r="G2" s="1">
         <v>800</v>
       </c>
-      <c r="H2" s="1">
-        <f t="shared" ref="H2:H11" si="0">SUM(D2:G2)</f>
-        <v>7103</v>
-      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
@@ -592,10 +588,6 @@
       <c r="G3" s="1">
         <v>500</v>
       </c>
-      <c r="H3" s="1">
-        <f t="shared" si="0"/>
-        <v>4905</v>
-      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
@@ -619,10 +611,6 @@
       <c r="G4" s="1">
         <v>800</v>
       </c>
-      <c r="H4" s="1">
-        <f t="shared" si="0"/>
-        <v>5362</v>
-      </c>
       <c r="K4" s="1" t="s">
         <v>25</v>
       </c>
@@ -652,10 +640,6 @@
       <c r="G5" s="1">
         <v>1000</v>
       </c>
-      <c r="H5" s="1">
-        <f t="shared" si="0"/>
-        <v>8095.5</v>
-      </c>
       <c r="K5" s="1" t="s">
         <v>27</v>
       </c>
@@ -685,10 +669,6 @@
       <c r="G6" s="1">
         <v>1000</v>
       </c>
-      <c r="H6" s="1">
-        <f t="shared" si="0"/>
-        <v>7100.5</v>
-      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
@@ -712,10 +692,6 @@
       <c r="G7" s="1">
         <v>800</v>
       </c>
-      <c r="H7" s="1">
-        <f t="shared" si="0"/>
-        <v>5750.3000030517578</v>
-      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
@@ -739,10 +715,6 @@
       <c r="G8" s="1">
         <v>480</v>
       </c>
-      <c r="H8" s="1">
-        <f t="shared" si="0"/>
-        <v>6390.5</v>
-      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
@@ -766,10 +738,6 @@
       <c r="G9" s="1">
         <v>900</v>
       </c>
-      <c r="H9" s="1">
-        <f t="shared" si="0"/>
-        <v>6998.5</v>
-      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
@@ -793,10 +761,6 @@
       <c r="G10" s="1">
         <v>600</v>
       </c>
-      <c r="H10" s="1">
-        <f t="shared" si="0"/>
-        <v>7354</v>
-      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
@@ -819,10 +783,6 @@
       </c>
       <c r="G11" s="1">
         <v>800</v>
-      </c>
-      <c r="H11" s="1">
-        <f t="shared" si="0"/>
-        <v>5610.1999969482422</v>
       </c>
     </row>
   </sheetData>
